--- a/outputs/Block2_Popular_Vote_Methods_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Methods_v12.xlsx
@@ -524,13 +524,13 @@
         <v>4.526479999999951</v>
       </c>
       <c r="C6">
-        <v>4.666221474017744</v>
+        <v>4.666221474017745</v>
       </c>
       <c r="D6">
         <v>2.919999999999996</v>
       </c>
       <c r="E6">
-        <v>2.878160000000125</v>
+        <v>2.878160000000127</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -541,7 +541,7 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>5.273583577922919</v>
+        <v>5.27358357792292</v>
       </c>
       <c r="C7">
         <v>5.432665386242507</v>
@@ -550,7 +550,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E7">
-        <v>2.905332478545527</v>
+        <v>2.905332478545524</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -561,16 +561,16 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>6.105200000000002</v>
+        <v>6.105200000000003</v>
       </c>
       <c r="C8">
-        <v>6.287706569606075</v>
+        <v>6.287706569606076</v>
       </c>
       <c r="D8">
         <v>2.919999999999996</v>
       </c>
       <c r="E8">
-        <v>2.928560000000146</v>
+        <v>2.928560000000143</v>
       </c>
       <c r="F8">
         <v>5</v>
